--- a/Employee_Reports_wi52/Murshidul Haq Patteri Thazhe Kuni Q0566.xlsx
+++ b/Employee_Reports_wi52/Murshidul Haq Patteri Thazhe Kuni Q0566.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -526,25 +526,62 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>YOU ARE LISTED AS ; IT TEAM</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>&amp; THIS IS YOUR TRAINING DASHBOARD</t>
-        </is>
-      </c>
+          <t>IS0 55001 (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>23-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>22-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>725</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>YOU ARE LISTED AS ; IT TEAM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>&amp; THIS IS YOUR TRAINING DASHBOARD</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
